--- a/BOM/JLCPCB.xlsx
+++ b/BOM/JLCPCB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\matthewgraff-arduinomegapcb\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F75B577-BCD3-4216-9F83-90468BA74085}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7178932A-0B6E-407F-9431-14E79BADA510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="236">
   <si>
     <t>Comment</t>
   </si>
@@ -115,9 +115,6 @@
     <t>BH254V-10P ( JTAG 2.54mm)</t>
   </si>
   <si>
-    <t>ICSP</t>
-  </si>
-  <si>
     <t>DM3BT-DSF-PEJS</t>
   </si>
   <si>
@@ -133,15 +130,6 @@
     <t>Yellow</t>
   </si>
   <si>
-    <t>1.5inch RGB OLED</t>
-  </si>
-  <si>
-    <t>OLED Module</t>
-  </si>
-  <si>
-    <t>TEST POINT</t>
-  </si>
-  <si>
     <t>MMBT3904M</t>
   </si>
   <si>
@@ -196,9 +184,6 @@
     <t>100K</t>
   </si>
   <si>
-    <t>Solder Bridge</t>
-  </si>
-  <si>
     <t>Tactile Switch</t>
   </si>
   <si>
@@ -325,9 +310,6 @@
     <t>J12</t>
   </si>
   <si>
-    <t>J13</t>
-  </si>
-  <si>
     <t>J14</t>
   </si>
   <si>
@@ -346,15 +328,6 @@
     <t>LED4, LED6, LED8, LED9</t>
   </si>
   <si>
-    <t>LED5</t>
-  </si>
-  <si>
-    <t>LED7</t>
-  </si>
-  <si>
-    <t>P1, P2, P3, P4, P5, P6</t>
-  </si>
-  <si>
     <t>Q1, Q2, Q3, Q4</t>
   </si>
   <si>
@@ -412,9 +385,6 @@
     <t>R48</t>
   </si>
   <si>
-    <t>SB1, SB2</t>
-  </si>
-  <si>
     <t>SW1</t>
   </si>
   <si>
@@ -511,9 +481,6 @@
     <t>BH254V-10P</t>
   </si>
   <si>
-    <t>BH254V-6P</t>
-  </si>
-  <si>
     <t>SMRH74-220MT</t>
   </si>
   <si>
@@ -526,12 +493,6 @@
     <t>LED-0603</t>
   </si>
   <si>
-    <t>ZIO-101954</t>
-  </si>
-  <si>
-    <t>Test-point</t>
-  </si>
-  <si>
     <t>SOT-723</t>
   </si>
   <si>
@@ -758,9 +719,6 @@
   </si>
   <si>
     <t>C13738</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
   <si>
     <t>C114765</t>
@@ -825,7 +783,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -907,33 +865,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -954,12 +890,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1249,7 +1179,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D72"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -1263,13 +1193,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -1277,13 +1207,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="36" x14ac:dyDescent="0.25">
@@ -1291,13 +1221,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1305,13 +1235,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1319,13 +1249,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1333,13 +1263,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="24" x14ac:dyDescent="0.25">
@@ -1347,13 +1277,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1361,13 +1291,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1375,13 +1305,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1389,13 +1319,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1403,13 +1333,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1417,13 +1347,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1431,13 +1361,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1445,13 +1375,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1459,13 +1389,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1473,13 +1403,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1487,13 +1417,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1501,13 +1431,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1515,13 +1445,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1529,13 +1459,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1543,13 +1473,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1557,13 +1487,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1571,13 +1501,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1585,13 +1515,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1599,13 +1529,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1613,13 +1543,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1627,13 +1557,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C27" s="7">
         <v>1051330011</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1641,13 +1571,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>27</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1655,13 +1585,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1669,13 +1599,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="24" x14ac:dyDescent="0.25">
@@ -1683,13 +1613,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1697,13 +1627,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>163</v>
+        <v>31</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>246</v>
+        <v>199</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1711,27 +1641,27 @@
         <v>32</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>32</v>
+        <v>153</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1739,13 +1669,13 @@
         <v>33</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1753,13 +1683,13 @@
         <v>34</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1767,13 +1697,13 @@
         <v>35</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1781,13 +1711,13 @@
         <v>36</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1795,13 +1725,13 @@
         <v>37</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>37</v>
+        <v>158</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>246</v>
+        <v>206</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1809,27 +1739,27 @@
         <v>38</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="24" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
         <v>39</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>246</v>
+        <v>208</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1837,13 +1767,13 @@
         <v>40</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1851,13 +1781,13 @@
         <v>41</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1865,27 +1795,27 @@
         <v>42</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" ht="24" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1893,13 +1823,13 @@
         <v>44</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -1907,13 +1837,13 @@
         <v>45</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -1921,13 +1851,13 @@
         <v>46</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -1935,13 +1865,13 @@
         <v>47</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -1949,13 +1879,13 @@
         <v>48</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -1963,13 +1893,13 @@
         <v>49</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -1977,13 +1907,13 @@
         <v>50</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -1991,13 +1921,13 @@
         <v>51</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -2005,83 +1935,83 @@
         <v>52</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>247</v>
+        <v>224</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -2089,13 +2019,13 @@
         <v>57</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -2103,13 +2033,13 @@
         <v>58</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>58</v>
+        <v>164</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>246</v>
+        <v>226</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -2117,13 +2047,13 @@
         <v>59</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -2131,13 +2061,13 @@
         <v>60</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -2145,13 +2075,13 @@
         <v>61</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -2159,13 +2089,13 @@
         <v>62</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -2173,13 +2103,13 @@
         <v>63</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -2187,83 +2117,13 @@
         <v>64</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B68" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="C69" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D69" s="6" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B70" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="C70" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="D70" s="4" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="C71" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="D71" s="6" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="B72" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="C72" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="D72" s="8" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
